--- a/logs/irCLIP.xlsx
+++ b/logs/irCLIP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikej\Documents\Career\Georges\Ule\intron_retention_propensity\logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6507854-A806-43F5-86B3-BE47608131DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D854EA99-9EE6-475C-846D-3A1FC4250CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1560" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="irCLIP" sheetId="1" r:id="rId1"/>
@@ -977,15 +977,6 @@
     <t>GSM8371117</t>
   </si>
   <si>
-    <t>60–120 kDa</t>
-  </si>
-  <si>
-    <t>120–225 kDa</t>
-  </si>
-  <si>
-    <t>225–350 kDa</t>
-  </si>
-  <si>
     <t>Purification Target Annotation</t>
   </si>
   <si>
@@ -1356,6 +1347,15 @@
   </si>
   <si>
     <t>ACTGACTGAC</t>
+  </si>
+  <si>
+    <t>60-120kDa</t>
+  </si>
+  <si>
+    <t>120-225kDa</t>
+  </si>
+  <si>
+    <t>225-350kDa</t>
   </si>
 </sst>
 </file>
@@ -1827,8 +1827,8 @@
     <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.28515625" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="7" max="7" width="65.42578125" customWidth="1"/>
+    <col min="8" max="8" width="28.140625" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="21.140625" customWidth="1"/>
     <col min="11" max="11" width="19.140625" customWidth="1"/>
@@ -1932,7 +1932,7 @@
         <v>26</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
@@ -2043,7 +2043,7 @@
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B4" t="s">
         <v>154</v>
@@ -2073,7 +2073,7 @@
         <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>314</v>
+        <v>438</v>
       </c>
       <c r="L4" t="s">
         <v>56</v>
@@ -2099,7 +2099,7 @@
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B5" t="s">
         <v>153</v>
@@ -2129,7 +2129,7 @@
         <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>315</v>
+        <v>439</v>
       </c>
       <c r="L5" t="s">
         <v>52</v>
@@ -2155,7 +2155,7 @@
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B6" t="s">
         <v>152</v>
@@ -2185,7 +2185,7 @@
         <v>35</v>
       </c>
       <c r="K6" t="s">
-        <v>316</v>
+        <v>440</v>
       </c>
       <c r="L6" t="s">
         <v>53</v>
@@ -2211,7 +2211,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B7" t="s">
         <v>151</v>
@@ -2241,7 +2241,7 @@
         <v>35</v>
       </c>
       <c r="K7" t="s">
-        <v>314</v>
+        <v>438</v>
       </c>
       <c r="L7" t="s">
         <v>56</v>
@@ -2267,7 +2267,7 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B8" t="s">
         <v>150</v>
@@ -2297,7 +2297,7 @@
         <v>35</v>
       </c>
       <c r="K8" t="s">
-        <v>315</v>
+        <v>439</v>
       </c>
       <c r="L8" t="s">
         <v>52</v>
@@ -2323,7 +2323,7 @@
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B9" t="s">
         <v>149</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B10" t="s">
         <v>148</v>
@@ -2406,7 +2406,7 @@
         <v>35</v>
       </c>
       <c r="K10" t="s">
-        <v>316</v>
+        <v>440</v>
       </c>
       <c r="L10" t="s">
         <v>53</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B11" t="s">
         <v>147</v>
@@ -2485,7 +2485,7 @@
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B12" t="s">
         <v>146</v>
@@ -2515,7 +2515,7 @@
         <v>35</v>
       </c>
       <c r="K12" t="s">
-        <v>314</v>
+        <v>438</v>
       </c>
       <c r="L12" t="s">
         <v>56</v>
@@ -2541,7 +2541,7 @@
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B13" t="s">
         <v>145</v>
@@ -2571,7 +2571,7 @@
         <v>35</v>
       </c>
       <c r="K13" t="s">
-        <v>315</v>
+        <v>439</v>
       </c>
       <c r="L13" t="s">
         <v>52</v>
@@ -2597,7 +2597,7 @@
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B14" t="s">
         <v>144</v>
@@ -2627,7 +2627,7 @@
         <v>35</v>
       </c>
       <c r="K14" t="s">
-        <v>316</v>
+        <v>440</v>
       </c>
       <c r="L14" t="s">
         <v>53</v>
@@ -2653,7 +2653,7 @@
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B15" t="s">
         <v>143</v>
@@ -2683,7 +2683,7 @@
         <v>35</v>
       </c>
       <c r="K15" t="s">
-        <v>314</v>
+        <v>438</v>
       </c>
       <c r="L15" t="s">
         <v>56</v>
@@ -2709,7 +2709,7 @@
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B16" t="s">
         <v>142</v>
@@ -2739,7 +2739,7 @@
         <v>35</v>
       </c>
       <c r="K16" t="s">
-        <v>315</v>
+        <v>439</v>
       </c>
       <c r="L16" t="s">
         <v>52</v>
@@ -2765,7 +2765,7 @@
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B17" t="s">
         <v>141</v>
@@ -2795,7 +2795,7 @@
         <v>35</v>
       </c>
       <c r="K17" t="s">
-        <v>316</v>
+        <v>440</v>
       </c>
       <c r="L17" t="s">
         <v>53</v>
@@ -2821,7 +2821,7 @@
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B18" t="s">
         <v>140</v>
@@ -2877,7 +2877,7 @@
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B19" t="s">
         <v>139</v>
@@ -2928,12 +2928,12 @@
         <v>39</v>
       </c>
       <c r="AB19" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B20" t="s">
         <v>138</v>
@@ -2981,15 +2981,15 @@
         <v>28</v>
       </c>
       <c r="AA20" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AB20" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B21" t="s">
         <v>137</v>
@@ -3037,15 +3037,15 @@
         <v>28</v>
       </c>
       <c r="AA21" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AB21" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B22" t="s">
         <v>136</v>
@@ -3075,7 +3075,7 @@
         <v>35</v>
       </c>
       <c r="K22" t="s">
-        <v>314</v>
+        <v>438</v>
       </c>
       <c r="L22" t="s">
         <v>55</v>
@@ -3096,15 +3096,15 @@
         <v>28</v>
       </c>
       <c r="AA22" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AB22" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B23" t="s">
         <v>135</v>
@@ -3134,7 +3134,7 @@
         <v>35</v>
       </c>
       <c r="K23" t="s">
-        <v>315</v>
+        <v>439</v>
       </c>
       <c r="L23" t="s">
         <v>54</v>
@@ -3155,15 +3155,15 @@
         <v>28</v>
       </c>
       <c r="AA23" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AB23" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B24" t="s">
         <v>134</v>
@@ -3193,7 +3193,7 @@
         <v>35</v>
       </c>
       <c r="K24" t="s">
-        <v>316</v>
+        <v>440</v>
       </c>
       <c r="L24" t="s">
         <v>49</v>
@@ -3214,15 +3214,15 @@
         <v>28</v>
       </c>
       <c r="AA24" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AB24" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B25" t="s">
         <v>133</v>
@@ -3252,7 +3252,7 @@
         <v>35</v>
       </c>
       <c r="K25" t="s">
-        <v>314</v>
+        <v>438</v>
       </c>
       <c r="L25" t="s">
         <v>55</v>
@@ -3273,15 +3273,15 @@
         <v>28</v>
       </c>
       <c r="AA25" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AB25" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B26" t="s">
         <v>132</v>
@@ -3311,7 +3311,7 @@
         <v>35</v>
       </c>
       <c r="K26" t="s">
-        <v>315</v>
+        <v>439</v>
       </c>
       <c r="L26" t="s">
         <v>54</v>
@@ -3332,15 +3332,15 @@
         <v>28</v>
       </c>
       <c r="AA26" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AB26" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B27" t="s">
         <v>131</v>
@@ -3370,7 +3370,7 @@
         <v>35</v>
       </c>
       <c r="K27" t="s">
-        <v>316</v>
+        <v>440</v>
       </c>
       <c r="L27" t="s">
         <v>49</v>
@@ -3391,15 +3391,15 @@
         <v>28</v>
       </c>
       <c r="AA27" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AB27" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B28" t="s">
         <v>130</v>
@@ -3452,7 +3452,7 @@
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B29" t="s">
         <v>129</v>
@@ -3505,7 +3505,7 @@
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B30" t="s">
         <v>128</v>
@@ -3535,7 +3535,7 @@
         <v>35</v>
       </c>
       <c r="K30" t="s">
-        <v>314</v>
+        <v>438</v>
       </c>
       <c r="L30" t="s">
         <v>56</v>
@@ -3561,7 +3561,7 @@
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B31" t="s">
         <v>127</v>
@@ -3591,7 +3591,7 @@
         <v>35</v>
       </c>
       <c r="K31" t="s">
-        <v>315</v>
+        <v>439</v>
       </c>
       <c r="L31" t="s">
         <v>52</v>
@@ -3617,7 +3617,7 @@
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B32" t="s">
         <v>126</v>
@@ -3647,7 +3647,7 @@
         <v>35</v>
       </c>
       <c r="K32" t="s">
-        <v>316</v>
+        <v>440</v>
       </c>
       <c r="L32" t="s">
         <v>53</v>
@@ -3673,7 +3673,7 @@
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B33" t="s">
         <v>125</v>
@@ -3703,7 +3703,7 @@
         <v>35</v>
       </c>
       <c r="K33" t="s">
-        <v>314</v>
+        <v>438</v>
       </c>
       <c r="L33" t="s">
         <v>56</v>
@@ -3729,7 +3729,7 @@
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B34" t="s">
         <v>124</v>
@@ -3759,7 +3759,7 @@
         <v>35</v>
       </c>
       <c r="K34" t="s">
-        <v>315</v>
+        <v>439</v>
       </c>
       <c r="L34" t="s">
         <v>52</v>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B35" t="s">
         <v>123</v>
@@ -3815,7 +3815,7 @@
         <v>34</v>
       </c>
       <c r="K35" t="s">
-        <v>314</v>
+        <v>438</v>
       </c>
       <c r="L35" t="s">
         <v>45</v>
@@ -3841,7 +3841,7 @@
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B36" t="s">
         <v>122</v>
@@ -3871,7 +3871,7 @@
         <v>34</v>
       </c>
       <c r="K36" t="s">
-        <v>315</v>
+        <v>439</v>
       </c>
       <c r="L36" t="s">
         <v>47</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B37" t="s">
         <v>121</v>
@@ -3927,7 +3927,7 @@
         <v>34</v>
       </c>
       <c r="K37" t="s">
-        <v>316</v>
+        <v>440</v>
       </c>
       <c r="L37" t="s">
         <v>46</v>
@@ -3953,7 +3953,7 @@
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B38" t="s">
         <v>120</v>
@@ -4009,7 +4009,7 @@
     </row>
     <row r="39" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B39" t="s">
         <v>119</v>
@@ -4065,7 +4065,7 @@
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B40" t="s">
         <v>118</v>
@@ -4118,7 +4118,7 @@
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B41" t="s">
         <v>117</v>
@@ -4171,7 +4171,7 @@
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B42" t="s">
         <v>116</v>
@@ -4201,7 +4201,7 @@
         <v>34</v>
       </c>
       <c r="K42" t="s">
-        <v>314</v>
+        <v>438</v>
       </c>
       <c r="L42" t="s">
         <v>55</v>
@@ -4227,7 +4227,7 @@
     </row>
     <row r="43" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B43" t="s">
         <v>115</v>
@@ -4257,7 +4257,7 @@
         <v>34</v>
       </c>
       <c r="K43" t="s">
-        <v>315</v>
+        <v>439</v>
       </c>
       <c r="L43" t="s">
         <v>54</v>
@@ -4283,7 +4283,7 @@
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B44" t="s">
         <v>114</v>
@@ -4313,7 +4313,7 @@
         <v>34</v>
       </c>
       <c r="K44" t="s">
-        <v>316</v>
+        <v>440</v>
       </c>
       <c r="L44" t="s">
         <v>49</v>
@@ -4339,7 +4339,7 @@
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B45" t="s">
         <v>113</v>
@@ -4369,7 +4369,7 @@
         <v>34</v>
       </c>
       <c r="K45" t="s">
-        <v>314</v>
+        <v>438</v>
       </c>
       <c r="L45" t="s">
         <v>55</v>
@@ -4395,7 +4395,7 @@
     </row>
     <row r="46" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B46" t="s">
         <v>112</v>
@@ -4425,7 +4425,7 @@
         <v>34</v>
       </c>
       <c r="K46" t="s">
-        <v>315</v>
+        <v>439</v>
       </c>
       <c r="L46" t="s">
         <v>54</v>
@@ -4451,7 +4451,7 @@
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B47" t="s">
         <v>111</v>
@@ -4481,7 +4481,7 @@
         <v>34</v>
       </c>
       <c r="K47" t="s">
-        <v>316</v>
+        <v>440</v>
       </c>
       <c r="L47" t="s">
         <v>49</v>
@@ -4507,7 +4507,7 @@
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B48" t="s">
         <v>110</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="49" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s">
         <v>109</v>
@@ -4613,7 +4613,7 @@
     </row>
     <row r="50" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B50" t="s">
         <v>108</v>
@@ -4666,7 +4666,7 @@
     </row>
     <row r="51" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B51" t="s">
         <v>107</v>
@@ -4696,7 +4696,7 @@
         <v>35</v>
       </c>
       <c r="L51" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="U51" t="s">
         <v>264</v>
@@ -4719,7 +4719,7 @@
     </row>
     <row r="52" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B52" t="s">
         <v>106</v>
@@ -4749,7 +4749,7 @@
         <v>35</v>
       </c>
       <c r="L52" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="U52" t="s">
         <v>263</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="53" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B53" t="s">
         <v>105</v>
@@ -4828,7 +4828,7 @@
     </row>
     <row r="54" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B54" t="s">
         <v>104</v>
@@ -4858,7 +4858,7 @@
         <v>35</v>
       </c>
       <c r="L54" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="U54" t="s">
         <v>261</v>
@@ -4881,7 +4881,7 @@
     </row>
     <row r="55" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B55" t="s">
         <v>103</v>
@@ -4911,7 +4911,7 @@
         <v>35</v>
       </c>
       <c r="L55" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="U55" t="s">
         <v>260</v>
@@ -4934,7 +4934,7 @@
     </row>
     <row r="56" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B56" t="s">
         <v>102</v>
@@ -4964,7 +4964,7 @@
         <v>35</v>
       </c>
       <c r="L56" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="U56" t="s">
         <v>259</v>
@@ -4987,7 +4987,7 @@
     </row>
     <row r="57" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B57" t="s">
         <v>101</v>
@@ -5017,7 +5017,7 @@
         <v>35</v>
       </c>
       <c r="L57" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="U57" t="s">
         <v>258</v>
@@ -5040,7 +5040,7 @@
     </row>
     <row r="58" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B58" t="s">
         <v>100</v>
@@ -5070,7 +5070,7 @@
         <v>35</v>
       </c>
       <c r="L58" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="U58" t="s">
         <v>257</v>
@@ -5093,7 +5093,7 @@
     </row>
     <row r="59" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B59" t="s">
         <v>99</v>
@@ -5123,7 +5123,7 @@
         <v>35</v>
       </c>
       <c r="L59" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="U59" t="s">
         <v>256</v>
@@ -5146,7 +5146,7 @@
     </row>
     <row r="60" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B60" t="s">
         <v>197</v>
@@ -5197,12 +5197,12 @@
         <v>39</v>
       </c>
       <c r="AB60" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="61" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B61" t="s">
         <v>196</v>
@@ -5253,12 +5253,12 @@
         <v>39</v>
       </c>
       <c r="AB61" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="62" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B62" t="s">
         <v>195</v>
@@ -5309,12 +5309,12 @@
         <v>39</v>
       </c>
       <c r="AB62" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="63" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B63" t="s">
         <v>194</v>
@@ -5365,12 +5365,12 @@
         <v>39</v>
       </c>
       <c r="AB63" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="64" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B64" t="s">
         <v>98</v>
@@ -5421,12 +5421,12 @@
         <v>39</v>
       </c>
       <c r="AB64" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="65" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B65" t="s">
         <v>97</v>
@@ -5477,12 +5477,12 @@
         <v>39</v>
       </c>
       <c r="AB65" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="66" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B66" t="s">
         <v>96</v>
@@ -5533,12 +5533,12 @@
         <v>39</v>
       </c>
       <c r="AB66" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="67" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B67" t="s">
         <v>95</v>
@@ -5591,7 +5591,7 @@
     </row>
     <row r="68" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B68" t="s">
         <v>94</v>
@@ -5644,7 +5644,7 @@
     </row>
     <row r="69" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B69" t="s">
         <v>93</v>
@@ -5697,7 +5697,7 @@
     </row>
     <row r="70" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B70" t="s">
         <v>92</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="71" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B71" t="s">
         <v>91</v>
@@ -5803,7 +5803,7 @@
     </row>
     <row r="72" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B72" t="s">
         <v>90</v>
@@ -5859,7 +5859,7 @@
     </row>
     <row r="73" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B73" t="s">
         <v>89</v>
@@ -5915,7 +5915,7 @@
     </row>
     <row r="74" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B74" t="s">
         <v>88</v>
@@ -5971,7 +5971,7 @@
     </row>
     <row r="75" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B75" t="s">
         <v>87</v>
@@ -6027,7 +6027,7 @@
     </row>
     <row r="76" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B76" t="s">
         <v>86</v>
@@ -6083,7 +6083,7 @@
     </row>
     <row r="77" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B77" t="s">
         <v>85</v>
@@ -6139,7 +6139,7 @@
     </row>
     <row r="78" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B78" t="s">
         <v>193</v>
@@ -6192,7 +6192,7 @@
     </row>
     <row r="79" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B79" t="s">
         <v>192</v>
@@ -6245,7 +6245,7 @@
     </row>
     <row r="80" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B80" t="s">
         <v>191</v>
@@ -6298,7 +6298,7 @@
     </row>
     <row r="81" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B81" t="s">
         <v>190</v>
@@ -6349,12 +6349,12 @@
         <v>37</v>
       </c>
       <c r="AB81" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="82" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B82" t="s">
         <v>189</v>
@@ -6405,12 +6405,12 @@
         <v>37</v>
       </c>
       <c r="AB82" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="83" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B83" t="s">
         <v>84</v>
@@ -6440,7 +6440,7 @@
         <v>35</v>
       </c>
       <c r="K83" t="s">
-        <v>316</v>
+        <v>440</v>
       </c>
       <c r="L83" t="s">
         <v>53</v>
@@ -6466,7 +6466,7 @@
     </row>
     <row r="84" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B84" t="s">
         <v>83</v>
@@ -6522,7 +6522,7 @@
     </row>
     <row r="85" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B85" t="s">
         <v>82</v>
@@ -6578,7 +6578,7 @@
     </row>
     <row r="86" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B86" t="s">
         <v>81</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="87" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B87" t="s">
         <v>81</v>
@@ -6684,7 +6684,7 @@
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B88" t="s">
         <v>80</v>
@@ -6714,7 +6714,7 @@
         <v>35</v>
       </c>
       <c r="K88" t="s">
-        <v>314</v>
+        <v>438</v>
       </c>
       <c r="L88" t="s">
         <v>48</v>
@@ -6740,7 +6740,7 @@
     </row>
     <row r="89" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B89" t="s">
         <v>79</v>
@@ -6770,7 +6770,7 @@
         <v>35</v>
       </c>
       <c r="K89" t="s">
-        <v>315</v>
+        <v>439</v>
       </c>
       <c r="L89" t="s">
         <v>51</v>
@@ -6796,7 +6796,7 @@
     </row>
     <row r="90" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B90" t="s">
         <v>78</v>
@@ -6826,7 +6826,7 @@
         <v>35</v>
       </c>
       <c r="K90" t="s">
-        <v>316</v>
+        <v>440</v>
       </c>
       <c r="L90" t="s">
         <v>50</v>
@@ -6852,7 +6852,7 @@
     </row>
     <row r="91" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B91" t="s">
         <v>77</v>
@@ -6882,7 +6882,7 @@
         <v>35</v>
       </c>
       <c r="K91" t="s">
-        <v>314</v>
+        <v>438</v>
       </c>
       <c r="L91" t="s">
         <v>48</v>
@@ -6908,7 +6908,7 @@
     </row>
     <row r="92" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B92" t="s">
         <v>76</v>
@@ -6938,7 +6938,7 @@
         <v>35</v>
       </c>
       <c r="K92" t="s">
-        <v>315</v>
+        <v>439</v>
       </c>
       <c r="L92" t="s">
         <v>51</v>
@@ -6964,7 +6964,7 @@
     </row>
     <row r="93" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B93" t="s">
         <v>75</v>
@@ -6994,7 +6994,7 @@
         <v>35</v>
       </c>
       <c r="K93" t="s">
-        <v>316</v>
+        <v>440</v>
       </c>
       <c r="L93" t="s">
         <v>50</v>
@@ -7020,7 +7020,7 @@
     </row>
     <row r="94" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B94" t="s">
         <v>74</v>
@@ -7068,12 +7068,12 @@
         <v>28</v>
       </c>
       <c r="AA94" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="95" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B95" t="s">
         <v>73</v>
@@ -7121,12 +7121,12 @@
         <v>28</v>
       </c>
       <c r="AA95" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="96" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B96" t="s">
         <v>72</v>
@@ -7156,7 +7156,7 @@
         <v>35</v>
       </c>
       <c r="K96" t="s">
-        <v>314</v>
+        <v>438</v>
       </c>
       <c r="L96" t="s">
         <v>45</v>
@@ -7177,12 +7177,12 @@
         <v>28</v>
       </c>
       <c r="AA96" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="97" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B97" t="s">
         <v>71</v>
@@ -7212,7 +7212,7 @@
         <v>35</v>
       </c>
       <c r="K97" t="s">
-        <v>315</v>
+        <v>439</v>
       </c>
       <c r="L97" t="s">
         <v>47</v>
@@ -7233,12 +7233,12 @@
         <v>28</v>
       </c>
       <c r="AA97" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="98" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B98" t="s">
         <v>70</v>
@@ -7268,7 +7268,7 @@
         <v>34</v>
       </c>
       <c r="K98" t="s">
-        <v>316</v>
+        <v>440</v>
       </c>
       <c r="L98" t="s">
         <v>46</v>
@@ -7289,12 +7289,12 @@
         <v>28</v>
       </c>
       <c r="AA98" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="99" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B99" t="s">
         <v>69</v>
@@ -7324,7 +7324,7 @@
         <v>34</v>
       </c>
       <c r="K99" t="s">
-        <v>314</v>
+        <v>438</v>
       </c>
       <c r="L99" t="s">
         <v>45</v>
@@ -7345,12 +7345,12 @@
         <v>28</v>
       </c>
       <c r="AA99" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="100" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B100" t="s">
         <v>68</v>
@@ -7380,7 +7380,7 @@
         <v>34</v>
       </c>
       <c r="K100" t="s">
-        <v>315</v>
+        <v>439</v>
       </c>
       <c r="L100" t="s">
         <v>47</v>
@@ -7401,12 +7401,12 @@
         <v>28</v>
       </c>
       <c r="AA100" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="101" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B101" t="s">
         <v>67</v>
@@ -7436,7 +7436,7 @@
         <v>34</v>
       </c>
       <c r="K101" t="s">
-        <v>316</v>
+        <v>440</v>
       </c>
       <c r="L101" t="s">
         <v>46</v>
@@ -7457,12 +7457,12 @@
         <v>28</v>
       </c>
       <c r="AA101" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="102" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B102" t="s">
         <v>66</v>
@@ -7518,7 +7518,7 @@
     </row>
     <row r="103" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B103" t="s">
         <v>65</v>
@@ -7574,7 +7574,7 @@
     </row>
     <row r="104" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B104" t="s">
         <v>188</v>
@@ -7625,12 +7625,12 @@
         <v>39</v>
       </c>
       <c r="AB104" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="105" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B105" t="s">
         <v>187</v>
@@ -7681,12 +7681,12 @@
         <v>39</v>
       </c>
       <c r="AB105" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="106" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B106" t="s">
         <v>186</v>
@@ -7737,12 +7737,12 @@
         <v>39</v>
       </c>
       <c r="AB106" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="107" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B107" t="s">
         <v>185</v>
@@ -7793,12 +7793,12 @@
         <v>39</v>
       </c>
       <c r="AB107" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="108" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B108" t="s">
         <v>184</v>
@@ -7849,12 +7849,12 @@
         <v>39</v>
       </c>
       <c r="AB108" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="109" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B109" t="s">
         <v>183</v>
@@ -7905,12 +7905,12 @@
         <v>39</v>
       </c>
       <c r="AB109" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="110" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B110" t="s">
         <v>64</v>
@@ -7963,7 +7963,7 @@
     </row>
     <row r="111" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B111" t="s">
         <v>63</v>
@@ -8016,7 +8016,7 @@
     </row>
     <row r="112" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B112" t="s">
         <v>62</v>
@@ -8046,7 +8046,7 @@
         <v>34</v>
       </c>
       <c r="K112" t="s">
-        <v>314</v>
+        <v>438</v>
       </c>
       <c r="L112" t="s">
         <v>45</v>
@@ -8072,7 +8072,7 @@
     </row>
     <row r="113" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B113" t="s">
         <v>61</v>
@@ -8102,7 +8102,7 @@
         <v>34</v>
       </c>
       <c r="K113" t="s">
-        <v>315</v>
+        <v>439</v>
       </c>
       <c r="L113" t="s">
         <v>47</v>
@@ -8128,7 +8128,7 @@
     </row>
     <row r="114" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B114" t="s">
         <v>60</v>
@@ -8158,7 +8158,7 @@
         <v>34</v>
       </c>
       <c r="K114" t="s">
-        <v>316</v>
+        <v>440</v>
       </c>
       <c r="L114" t="s">
         <v>46</v>
@@ -8184,7 +8184,7 @@
     </row>
     <row r="115" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B115" t="s">
         <v>182</v>
@@ -8235,12 +8235,12 @@
         <v>37</v>
       </c>
       <c r="AB115" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="116" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B116" t="s">
         <v>59</v>
@@ -8291,12 +8291,12 @@
         <v>37</v>
       </c>
       <c r="AB116" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="117" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B117" t="s">
         <v>58</v>
@@ -8347,7 +8347,7 @@
         <v>37</v>
       </c>
       <c r="AB117" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
